--- a/www/food_data_model.xlsx
+++ b/www/food_data_model.xlsx
@@ -1,21 +1,101 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hbrac\OneDrive\Documentos\Nutrição\Produtos\app\www\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{176BDB6E-61BD-475C-BC2A-ECB4EA278AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+  <si>
+    <t>food_group</t>
+  </si>
+  <si>
+    <t>food_name</t>
+  </si>
+  <si>
+    <t>food_id</t>
+  </si>
+  <si>
+    <t>CF_gCO2eq</t>
+  </si>
+  <si>
+    <t>WF_l</t>
+  </si>
+  <si>
+    <t>EF_g_m2</t>
+  </si>
+  <si>
+    <t>energy_kj_g</t>
+  </si>
+  <si>
+    <t>fat_g</t>
+  </si>
+  <si>
+    <t>sat_fat_g</t>
+  </si>
+  <si>
+    <t>CHO_g</t>
+  </si>
+  <si>
+    <t>sugars_g</t>
+  </si>
+  <si>
+    <t>fibre_g</t>
+  </si>
+  <si>
+    <t>protein_g</t>
+  </si>
+  <si>
+    <t>sodium_mg</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>Beverages</t>
+  </si>
+  <si>
+    <t>SUCO DE FRUTA OU VEGETAL ENCARTONADO</t>
+  </si>
+  <si>
+    <t>SUCO PARA VIAGEM</t>
+  </si>
+  <si>
+    <t>Dairy/alternatives</t>
+  </si>
+  <si>
+    <t>LEITE INTEGRAL DIETCOST</t>
+  </si>
+  <si>
+    <t>COALHADA</t>
+  </si>
+  <si>
+    <t>QUEIJO GORDO DIETCOST</t>
+  </si>
+  <si>
+    <t>REQUEIJAO DIETCOST</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +143,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +195,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +229,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +264,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,413 +440,336 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>food_group</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>food_name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>food_id</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>variety</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>CF_gCO2eq</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>WF_l</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>EF_g_m2</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>energy_kj_g</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>fat_g</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>sat_fat_g</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>CHO_g</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>sugars_g</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>fibre_g</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>protein_g</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>sodium_mg</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
+    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Beverages</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SUCO DE FRUTA OU VEGETAL ENCARTONADO</t>
-        </is>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
       </c>
       <c r="C2">
         <v>82047</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>205.00695999999999</v>
       </c>
       <c r="E2">
-        <v>205.00696</v>
+        <v>539.47108000000003</v>
       </c>
       <c r="F2">
-        <v>539.47108</v>
+        <v>2.4283581999999999</v>
       </c>
       <c r="G2">
-        <v>2.4283582</v>
+        <v>1585.65675814</v>
       </c>
       <c r="H2">
-        <v>1585.65675814</v>
+        <v>8.6000004000000008</v>
       </c>
       <c r="I2">
-        <v>8.600000400000001</v>
+        <v>1.5587289</v>
       </c>
       <c r="J2">
-        <v>1.5587289</v>
+        <v>64.5</v>
       </c>
       <c r="K2">
-        <v>64.5</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="M2">
-        <v>9.5</v>
+        <v>15.6</v>
       </c>
       <c r="N2">
-        <v>15.6</v>
+        <v>4.5927218999999999</v>
       </c>
       <c r="O2">
-        <v>4.5927219</v>
-      </c>
-      <c r="P2">
-        <v>1.008545281420033</v>
+        <v>1.0085452814200331</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Beverages</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>SUCO PARA VIAGEM</t>
-        </is>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
       </c>
       <c r="C3">
         <v>85004</v>
       </c>
       <c r="D3">
+        <v>249</v>
+      </c>
+      <c r="E3">
+        <v>799.09344999999996</v>
+      </c>
+      <c r="F3">
         <v>1</v>
       </c>
-      <c r="E3">
-        <v>249</v>
-      </c>
-      <c r="F3">
-        <v>799.09345</v>
-      </c>
       <c r="G3">
-        <v>1</v>
+        <v>1720.4459999999999</v>
       </c>
       <c r="H3">
-        <v>1720.446</v>
+        <v>15.07</v>
       </c>
       <c r="I3">
-        <v>15.07</v>
+        <v>2.9</v>
       </c>
       <c r="J3">
-        <v>2.9</v>
+        <v>62.05</v>
       </c>
       <c r="K3">
-        <v>62.05</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>7.83</v>
       </c>
       <c r="M3">
-        <v>7.83</v>
+        <v>10.68</v>
       </c>
       <c r="N3">
-        <v>10.68</v>
+        <v>125.95</v>
       </c>
       <c r="O3">
-        <v>125.95</v>
-      </c>
-      <c r="P3">
         <v>1.92472</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Dairy/alternatives</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LEITE INTEGRAL DIETCOST</t>
-        </is>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
       </c>
       <c r="C4">
         <v>79001</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2947.5</v>
       </c>
       <c r="E4">
-        <v>2947.5</v>
+        <v>1247.1093000000001</v>
       </c>
       <c r="F4">
-        <v>1247.1093</v>
+        <v>5.52</v>
       </c>
       <c r="G4">
-        <v>5.52</v>
+        <v>1776.5383581399999</v>
       </c>
       <c r="H4">
-        <v>1776.53835814</v>
+        <v>20.6</v>
       </c>
       <c r="I4">
-        <v>20.6</v>
+        <v>3.2259932</v>
       </c>
       <c r="J4">
-        <v>3.2259932</v>
+        <v>57.450001</v>
       </c>
       <c r="K4">
-        <v>57.450001</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M4">
-        <v>11</v>
+        <v>7.8000002000000004</v>
       </c>
       <c r="N4">
-        <v>7.8000002</v>
+        <v>608.21356000000003</v>
       </c>
       <c r="O4">
-        <v>608.21356</v>
-      </c>
-      <c r="P4">
-        <v>1.27801</v>
+        <v>1.2780100000000001</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Dairy/alternatives</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>COALHADA</t>
-        </is>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
       </c>
       <c r="C5">
         <v>79014</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2571.75</v>
       </c>
       <c r="E5">
-        <v>2571.75</v>
+        <v>2039.3333</v>
       </c>
       <c r="F5">
-        <v>2039.3333</v>
+        <v>13.54</v>
       </c>
       <c r="G5">
-        <v>13.54</v>
+        <v>37.125168935399998</v>
       </c>
       <c r="H5">
-        <v>37.1251689354</v>
+        <v>0.12444445</v>
       </c>
       <c r="I5">
-        <v>0.12444445</v>
+        <v>0.2</v>
       </c>
       <c r="J5">
-        <v>0.2</v>
+        <v>1.7912561</v>
       </c>
       <c r="K5">
-        <v>1.7912561</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1.8722221999999999</v>
       </c>
       <c r="M5">
-        <v>1.8722222</v>
+        <v>1.0820772999999999</v>
       </c>
       <c r="N5">
-        <v>1.0820773</v>
+        <v>4.2044443999999999</v>
       </c>
       <c r="O5">
-        <v>4.2044444</v>
-      </c>
-      <c r="P5">
         <v>1.032850913950579</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Dairy/alternatives</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>QUEIJO GORDO DIETCOST</t>
-        </is>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
       </c>
       <c r="C6">
         <v>79018</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>577.62404000000004</v>
       </c>
       <c r="E6">
-        <v>577.62404</v>
+        <v>2387.1860999999999</v>
       </c>
       <c r="F6">
-        <v>2387.1861</v>
+        <v>8.4</v>
       </c>
       <c r="G6">
-        <v>8.4</v>
+        <v>115.14290387600001</v>
       </c>
       <c r="H6">
-        <v>115.142903876</v>
+        <v>0.54666667999999996</v>
       </c>
       <c r="I6">
-        <v>0.54666668</v>
+        <v>0.12</v>
       </c>
       <c r="J6">
-        <v>0.12</v>
+        <v>4.3334785</v>
       </c>
       <c r="K6">
-        <v>4.3334785</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>3.1199998999999998</v>
       </c>
       <c r="M6">
-        <v>3.1199999</v>
+        <v>2.8731884999999999</v>
       </c>
       <c r="N6">
-        <v>2.8731885</v>
+        <v>9.0854997999999991</v>
       </c>
       <c r="O6">
-        <v>9.085499799999999</v>
-      </c>
-      <c r="P6">
-        <v>0.67259</v>
+        <v>0.67259000000000002</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Dairy/alternatives</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>REQUEIJAO DIETCOST</t>
-        </is>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
       </c>
       <c r="C7">
         <v>79029</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>443.4</v>
       </c>
       <c r="E7">
-        <v>443.4</v>
+        <v>1518.4430032697401</v>
       </c>
       <c r="F7">
-        <v>1518.44300326974</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>9</v>
+        <v>82.013041291999997</v>
       </c>
       <c r="H7">
-        <v>82.013041292</v>
+        <v>0.14111111000000001</v>
       </c>
       <c r="I7">
-        <v>0.14111111</v>
+        <v>4.7600000000000003E-2</v>
       </c>
       <c r="J7">
-        <v>0.0476</v>
+        <v>4.4199519</v>
       </c>
       <c r="K7">
-        <v>4.4199519</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.9233332999999999</v>
       </c>
       <c r="M7">
-        <v>1.9233333</v>
+        <v>1.1222706</v>
       </c>
       <c r="N7">
-        <v>1.1222706</v>
+        <v>3.3216667000000002</v>
       </c>
       <c r="O7">
-        <v>3.3216667</v>
-      </c>
-      <c r="P7">
         <v>0.24614</v>
       </c>
     </row>

--- a/www/food_data_model.xlsx
+++ b/www/food_data_model.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hbrac\OneDrive\Documentos\Nutrição\Produtos\app\www\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\x16610962\Proton Drive\hbracarense\Other computers\DESKTOP-1MJ2BL3\Documentos\Nutrição\Produtos\app\www\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{176BDB6E-61BD-475C-BC2A-ECB4EA278AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -94,7 +93,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -155,9 +154,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -195,9 +194,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -232,7 +231,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -267,7 +266,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -440,7 +439,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -523,7 +522,7 @@
         <v>64.5</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>2.4283581999999999</v>
       </c>
       <c r="L2">
         <v>9.5</v>
@@ -570,7 +569,7 @@
         <v>62.05</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>7.83</v>
@@ -617,7 +616,7 @@
         <v>57.450001</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="L4">
         <v>11</v>
@@ -664,7 +663,7 @@
         <v>1.7912561</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>13.54</v>
       </c>
       <c r="L5">
         <v>1.8722221999999999</v>
@@ -711,7 +710,7 @@
         <v>4.3334785</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="L6">
         <v>3.1199998999999998</v>
@@ -758,7 +757,7 @@
         <v>4.4199519</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L7">
         <v>1.9233332999999999</v>
